--- a/Result/profitability/2302.xlsx
+++ b/Result/profitability/2302.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13125</v>
+        <v>0.165</v>
       </c>
       <c r="N2" t="n">
-        <v>32.725</v>
+        <v>32.9675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.13375</v>
       </c>
       <c r="N3" t="n">
-        <v>30.27375</v>
+        <v>30.25875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07375000000000001</v>
+        <v>0.12375</v>
       </c>
       <c r="N4" t="n">
-        <v>26.42625</v>
+        <v>26.2875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.88</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.155</v>
+        <v>-0.12</v>
       </c>
       <c r="N5" t="n">
-        <v>20.9225</v>
+        <v>21.01375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.16625</v>
+        <v>-0.16875</v>
       </c>
       <c r="N6" t="n">
-        <v>18.7275</v>
+        <v>19.08625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.21375</v>
+        <v>-0.18125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.0825</v>
+        <v>16.29625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2175</v>
+        <v>-0.205</v>
       </c>
       <c r="N8" t="n">
-        <v>15.8775</v>
+        <v>16.50625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>284</v>
+      </c>
+      <c r="D75" t="n">
+        <v>177</v>
+      </c>
+      <c r="E75" t="n">
+        <v>107</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>55</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>59</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.19125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.36875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1537286063569683</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.999999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7299999999999969</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01971907077255519</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
